--- a/artfynd/A 69728-2021 artfynd.xlsx
+++ b/artfynd/A 69728-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69728-2021 artfynd.xlsx
+++ b/artfynd/A 69728-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY42"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304869</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304867</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304871</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304873</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304883</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304888</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304892</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1452,6 +1492,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304872</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1549,6 +1594,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304897</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914910</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1762,6 +1817,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304887</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1859,6 +1919,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304865</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1956,6 +2021,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304879</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2053,6 +2123,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304875</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2169,6 +2244,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914841</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,6 +2365,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914887</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2401,6 +2486,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914933</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914943</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2633,6 +2728,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914957</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2749,6 +2849,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914998</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2865,6 +2970,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87915011</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2962,6 +3072,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304866</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3059,6 +3174,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304870</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3156,6 +3276,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304876</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3253,6 +3378,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304877</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3350,6 +3480,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304878</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3447,6 +3582,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304886</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3544,6 +3684,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304889</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3641,6 +3786,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304890</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3738,6 +3888,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304895</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3835,6 +3990,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304898</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3932,6 +4092,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304899</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4029,6 +4194,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304882</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4155,6 +4325,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914866</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4276,6 +4451,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914973</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4397,6 +4577,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87914982</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4523,6 +4708,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87915043</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4620,6 +4810,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304874</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4717,6 +4912,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304885</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4814,6 +5014,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304894</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4911,8 +5116,56 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103304868</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>